--- a/docs/StructureDefinition-ImplantableDeviceDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDevice.xlsx
@@ -60,13 +60,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-17T15:32:01+00:00</t>
+    <t>2023-10-31T15:37:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>JPSys</t>
+    <t>VA</t>
   </si>
   <si>
     <t>Contact</t>

--- a/docs/StructureDefinition-ImplantableDeviceDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31T15:37:13+00:00</t>
+    <t>2023-11-01T18:52:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for Use Case Implantable Device, ResourceType Device</t>
+    <t>This StructureDefinition contains the maps for VistA ? (file ?) to FHIR Device</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-ImplantableDeviceDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-01T18:52:48+00:00</t>
+    <t>2023-11-08T21:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T21:21:15+00:00</t>
+    <t>2023-11-08T21:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-09T22:38:39+00:00</t>
+    <t>2023-11-14T14:54:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T14:54:31+00:00</t>
+    <t>2023-11-14T17:25:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T17:25:19+00:00</t>
+    <t>2023-11-15T12:04:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T12:04:59+00:00</t>
+    <t>2023-11-15T19:14:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T19:14:31+00:00</t>
+    <t>2023-11-15T20:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T20:37:43+00:00</t>
+    <t>2023-11-29T20:32:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T20:32:59+00:00</t>
+    <t>2023-11-29T21:08:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T21:08:10+00:00</t>
+    <t>2023-12-12T19:04:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-12T19:04:11+00:00</t>
+    <t>2023-12-21T07:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T07:51:53+00:00</t>
+    <t>2023-12-21T16:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.11.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T16:22:28+00:00</t>
+    <t>2023-12-28T09:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.11.0</t>
+    <t>0.12.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-28T09:08:39+00:00</t>
+    <t>2023-12-29T17:54:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.12.0</t>
+    <t>0.13.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T17:54:36+00:00</t>
+    <t>2024-01-03T19:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA ? (file ?) to FHIR Device</t>
+    <t>This StructureDefinition contains the maps for VistA file ? (#?) to us-core-implantable-device</t>
   </si>
   <si>
     <t>Purpose</t>
